--- a/tame_output/ON/bt/strategyON_20240516.xlsx
+++ b/tame_output/ON/bt/strategyON_20240516.xlsx
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382331</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.278199702495502</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347058</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.28737757613002</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207815</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879202</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.77376164710278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660767</v>
+        <v>3.733008865660768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002483</v>
+        <v>3.751143622002484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263901</v>
+        <v>3.741324873263902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481235</v>
+        <v>3.750725801481236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71698814345223</v>
+        <v>3.716988143452231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979537</v>
+        <v>3.737023032979538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230806</v>
+        <v>3.702305879230807</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285452</v>
+        <v>3.705568086285453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095068678481</v>
+        <v>3.709506867848101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106089760125</v>
+        <v>3.731060897601251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537862</v>
+        <v>3.722443786537863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.873049299145692</v>
+        <v>3.873049299145694</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.2043246616198</v>
+        <v>-4.20445067706248</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.190365472602267</v>
+        <v>1.190315066425195</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.2534707366187825</v>

--- a/tame_output/ON/bt/strategyON_20240516.xlsx
+++ b/tame_output/ON/bt/strategyON_20240516.xlsx
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-76.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.2%</t>
+          <t>111.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>130.1%</t>
+          <t>129.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.5%</t>
+          <t>-51.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.4%</t>
+          <t>-72.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-582.0%</t>
+          <t>-567.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.6%</t>
+          <t>-41.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>161.9%</t>
+          <t>162.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-257.2%</t>
+          <t>-251.3%</t>
         </is>
       </c>
     </row>
@@ -46746,10 +46746,10 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.20445067706248</v>
+        <v>-4.056830899550675</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.190315066425195</v>
+        <v>1.249362977429917</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.2534707366187825</v>

--- a/tame_output/ON/bt/strategyON_20240516.xlsx
+++ b/tame_output/ON/bt/strategyON_20240516.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>8.7%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.9%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>129.8%</t>
+          <t>130.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.9%</t>
+          <t>-53.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.8%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.0%</t>
+          <t>444.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-567.3%</t>
+          <t>-604.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.5%</t>
+          <t>-39.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>162.3%</t>
+          <t>161.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-251.3%</t>
+          <t>-266.1%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-189.1%</t>
+          <t>-188.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457902</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862985</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376164710278</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -46447,10 +46447,10 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.77692912287381</v>
+        <v>-4.001281012403902</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.193940476091003</v>
+        <v>1.104199720278966</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.09512622735346304</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660768</v>
+        <v>3.733008865660767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.863527705854913</v>
+        <v>-4.087879595385006</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.173814069000885</v>
+        <v>1.084073313188848</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.09512622735346304</v>
@@ -46493,10 +46493,10 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.825144043296762</v>
+        <v>-4.049495932826855</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.186586975366514</v>
+        <v>1.096846219554477</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.05674256479531187</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002484</v>
+        <v>3.751143622002483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.648027713261596</v>
+        <v>-3.872379602791689</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.254162536225882</v>
+        <v>1.164421780413845</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.05674256479531187</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263902</v>
+        <v>3.741324873263901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.618325589285302</v>
+        <v>-3.842677478815395</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.266726777578313</v>
+        <v>1.176986021766276</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.06121269001062524</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481236</v>
+        <v>3.750725801481235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.438950168046534</v>
+        <v>-3.663302057576628</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.332263921380235</v>
+        <v>1.242523165568197</v>
       </c>
       <c r="F1957" t="n">
         <v>0.09556406816009344</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452231</v>
+        <v>3.71698814345223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.48396438156714</v>
+        <v>-3.708316271097234</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.295065691303582</v>
+        <v>1.205324935491544</v>
       </c>
       <c r="F1958" t="n">
         <v>0.06521517284548883</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979538</v>
+        <v>3.737023032979537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.750968891839576</v>
+        <v>-3.975320781369669</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.193955449533553</v>
+        <v>1.104214693721516</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1291478651974597</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230807</v>
+        <v>3.702305879230806</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.039756112298491</v>
+        <v>-4.264108001828585</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.077644483246489</v>
+        <v>0.9879037274344511</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2302339852964601</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285453</v>
+        <v>3.705568086285452</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.007280526127719</v>
+        <v>-4.231632415657812</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.088234679269114</v>
+        <v>0.9984939234570769</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2302339852964601</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848101</v>
+        <v>3.7095068678481</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.988242398420422</v>
+        <v>-4.212594287950515</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.092374649560278</v>
+        <v>1.002633893748241</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.2884175966276546</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601251</v>
+        <v>3.73106089760125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.004988263676797</v>
+        <v>-4.22934015320689</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.263258172396408</v>
+        <v>1.173517416584371</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.2884175966276546</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537863</v>
+        <v>3.722443786537862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.057308644277589</v>
+        <v>-4.281660533807682</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.243163349142225</v>
+        <v>1.153422593330188</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.2534707366187825</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.873049299145694</v>
+        <v>3.367497805109939</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.056830899550675</v>
+        <v>-4.425983439732601</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.249362977429917</v>
+        <v>1.101701961357146</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.2534707366187825</v>

--- a/tame_output/ON/bt/strategyON_20240516.xlsx
+++ b/tame_output/ON/bt/strategyON_20240516.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>58.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-6.2%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-76.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,16 +926,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>130.1%</t>
+          <t>129.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.3%</t>
+          <t>-51.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-72.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.1%</t>
+          <t>449.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-10.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-604.2%</t>
+          <t>-567.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.3%</t>
+          <t>-41.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>161.2%</t>
+          <t>162.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-266.1%</t>
+          <t>-251.3%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-20.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-188.8%</t>
+          <t>-189.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-174.0%</t>
+          <t>-141.3%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1965"/>
+  <dimension ref="A1:G1966"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382331</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495502</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347058</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.28737757613002</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207815</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969594</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856158176096471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.77376164710278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837684</v>
+        <v>3.821589933837681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349963</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.818665376145936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009948</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046995</v>
+        <v>3.791269976046996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412103</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144514</v>
+        <v>3.762643902144515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900692</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978368</v>
+        <v>3.714175563978367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887702</v>
+        <v>3.710903155887699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460389506759</v>
+        <v>3.746038950675897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695445</v>
+        <v>3.765020747695442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199268</v>
+        <v>3.682712735199266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.001281012403902</v>
+        <v>-3.77692912287381</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.104199720278966</v>
+        <v>1.193940476091003</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.09512622735346304</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660767</v>
+        <v>3.733008865660766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.087879595385006</v>
+        <v>-3.863527705854913</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.084073313188848</v>
+        <v>1.173814069000885</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.09512622735346304</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.741170494383422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.049495932826855</v>
+        <v>-3.825144043296762</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.096846219554477</v>
+        <v>1.186586975366514</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.05674256479531187</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002483</v>
+        <v>3.751143622002481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.872379602791689</v>
+        <v>-3.648027713261596</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.164421780413845</v>
+        <v>1.254162536225882</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.05674256479531187</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263901</v>
+        <v>3.7413248732639</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.842677478815395</v>
+        <v>-3.618325589285302</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.176986021766276</v>
+        <v>1.266726777578313</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.06121269001062524</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481235</v>
+        <v>3.750725801481233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.663302057576628</v>
+        <v>-3.438950168046534</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.242523165568197</v>
+        <v>1.332263921380235</v>
       </c>
       <c r="F1957" t="n">
         <v>0.09556406816009344</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71698814345223</v>
+        <v>3.716988143452228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.708316271097234</v>
+        <v>-3.48396438156714</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.205324935491544</v>
+        <v>1.295065691303582</v>
       </c>
       <c r="F1958" t="n">
         <v>0.06521517284548883</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979537</v>
+        <v>3.737023032979535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.975320781369669</v>
+        <v>-3.750968891839576</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.104214693721516</v>
+        <v>1.193955449533553</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1291478651974597</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230806</v>
+        <v>3.702305879230808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.264108001828585</v>
+        <v>-4.039756112298491</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9879037274344511</v>
+        <v>1.077644483246489</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2302339852964601</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285452</v>
+        <v>3.705568086285454</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.231632415657812</v>
+        <v>-4.007280526127719</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9984939234570769</v>
+        <v>1.088234679269114</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2302339852964601</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095068678481</v>
+        <v>3.709506867848102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.212594287950515</v>
+        <v>-3.988242398420422</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.002633893748241</v>
+        <v>1.092374649560278</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.2884175966276546</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106089760125</v>
+        <v>3.731060897601251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.22934015320689</v>
+        <v>-4.004988263676797</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.173517416584371</v>
+        <v>1.263258172396408</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.2884175966276546</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537862</v>
+        <v>3.722443786537863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.281660533807682</v>
+        <v>-4.057308644277589</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.153422593330188</v>
+        <v>1.243163349142225</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.2534707366187825</v>
@@ -46740,22 +46740,45 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.367497805109939</v>
+        <v>3.787422005259125</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.425983439732601</v>
+        <v>-4.056830899550675</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.101701961357146</v>
+        <v>1.249362977429917</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.2534707366187825</v>
       </c>
       <c r="G1965" t="n">
         <v>2.720369319592665</v>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" s="2" t="n">
+        <v>45428</v>
+      </c>
+      <c r="B1966" t="n">
+        <v>3.867824864567725</v>
+      </c>
+      <c r="C1966" t="n">
+        <v>3.054623017229886</v>
+      </c>
+      <c r="D1966" t="n">
+        <v>-4.056830899550675</v>
+      </c>
+      <c r="E1966" t="n">
+        <v>1.249362977429917</v>
+      </c>
+      <c r="F1966" t="n">
+        <v>-0.2534707366187825</v>
+      </c>
+      <c r="G1966" t="n">
+        <v>3.047686814216254</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240516.xlsx
+++ b/tame_output/ON/bt/strategyON_20240516.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>11.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,42 +824,42 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-45.8%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.8%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.0%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.9%</t>
+          <t>-52.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.8%</t>
+          <t>-74.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.0%</t>
+          <t>444.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.4%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-567.3%</t>
+          <t>-588.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,37 +1140,37 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.5%</t>
+          <t>-38.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>162.3%</t>
+          <t>161.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-251.3%</t>
+          <t>-259.9%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-189.1%</t>
+          <t>-188.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-141.3%</t>
+          <t>-180.9%</t>
         </is>
       </c>
     </row>
@@ -46447,10 +46447,10 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.77692912287381</v>
+        <v>-3.991045259359882</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.193940476091003</v>
+        <v>1.108294021496574</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.09512622735346304</v>
@@ -46470,10 +46470,10 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.863527705854913</v>
+        <v>-4.077643842340985</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.173814069000885</v>
+        <v>1.088167614406456</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.09512622735346304</v>
@@ -46493,10 +46493,10 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.825144043296762</v>
+        <v>-4.039260179782834</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.186586975366514</v>
+        <v>1.100940520772085</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.05674256479531187</v>
@@ -46516,10 +46516,10 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.648027713261596</v>
+        <v>-3.862143849747667</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.254162536225882</v>
+        <v>1.168516081631454</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.05674256479531187</v>
@@ -46539,10 +46539,10 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.618325589285302</v>
+        <v>-3.832441725771374</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.266726777578313</v>
+        <v>1.181080322983884</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.06121269001062524</v>
@@ -46562,10 +46562,10 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.438950168046534</v>
+        <v>-3.653066304532606</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.332263921380235</v>
+        <v>1.246617466785806</v>
       </c>
       <c r="F1957" t="n">
         <v>0.09556406816009344</v>
@@ -46585,10 +46585,10 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.48396438156714</v>
+        <v>-3.698080518053212</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.295065691303582</v>
+        <v>1.209419236709153</v>
       </c>
       <c r="F1958" t="n">
         <v>0.06521517284548883</v>
@@ -46608,10 +46608,10 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.750968891839576</v>
+        <v>-3.965085028325648</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.193955449533553</v>
+        <v>1.108308994939124</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1291478651974597</v>
@@ -46631,10 +46631,10 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.039756112298491</v>
+        <v>-4.253872248784563</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.077644483246489</v>
+        <v>0.9919980286520598</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2302339852964601</v>
@@ -46654,10 +46654,10 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.007280526127719</v>
+        <v>-4.221396662613791</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.088234679269114</v>
+        <v>1.002588224674685</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2302339852964601</v>
@@ -46677,10 +46677,10 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.988242398420422</v>
+        <v>-4.202358534906494</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.092374649560278</v>
+        <v>1.006728194965849</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.2884175966276546</v>
@@ -46700,10 +46700,10 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.004988263676797</v>
+        <v>-4.219104400162869</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.263258172396408</v>
+        <v>1.17761171780198</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.2884175966276546</v>
@@ -46723,10 +46723,10 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.057308644277589</v>
+        <v>-4.271424780763661</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.243163349142225</v>
+        <v>1.157516894547796</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.2534707366187825</v>
@@ -46746,10 +46746,10 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.056830899550675</v>
+        <v>-4.270947036036747</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.249362977429917</v>
+        <v>1.163716522835488</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.2534707366187825</v>
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.867824864567725</v>
+        <v>3.393118917395605</v>
       </c>
       <c r="C1966" t="n">
-        <v>3.054623017229886</v>
+        <v>2.658449928184302</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.056830899550675</v>
+        <v>-4.270947036036747</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.249362977429917</v>
+        <v>1.163716522835488</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2534707366187825</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.047686814216254</v>
+        <v>2.65151372517067</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240516.xlsx
+++ b/tame_output/ON/bt/strategyON_20240516.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.8%</t>
+          <t>111.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>129.7%</t>
+          <t>130.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.7%</t>
+          <t>-53.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.4%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.8%</t>
+          <t>444.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-588.7%</t>
+          <t>-604.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>-39.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-259.9%</t>
+          <t>-266.1%</t>
         </is>
       </c>
     </row>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923088</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900556660786</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880273</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234398</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309723</v>
+        <v>3.833249172309724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858726</v>
+        <v>3.839370871858727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096471</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544779</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712291</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837681</v>
+        <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349963</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972336</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145936</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009948</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473599</v>
+        <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978367</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887699</v>
+        <v>3.710903155887702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675897</v>
+        <v>3.7460389506759</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695442</v>
+        <v>3.765020747695446</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.77320672158129</v>
+        <v>3.773206721581291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734159</v>
+        <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212295</v>
+        <v>3.786946382212297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786043</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273189</v>
+        <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279498</v>
+        <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030426</v>
+        <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942738</v>
+        <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268535</v>
+        <v>3.743044028268537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968861</v>
+        <v>3.689594264968862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175321</v>
+        <v>3.643066046175322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199266</v>
+        <v>3.682712735199268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.991045259359882</v>
+        <v>-4.001281012403902</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.108294021496574</v>
+        <v>1.104199720278966</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.09512622735346304</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660766</v>
+        <v>3.733008865660768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.077643842340985</v>
+        <v>-4.087879595385006</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.088167614406456</v>
+        <v>1.084073313188848</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.09512622735346304</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383422</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.039260179782834</v>
+        <v>-4.049495932826855</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.100940520772085</v>
+        <v>1.096846219554477</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.05674256479531187</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002481</v>
+        <v>3.751143622002484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.862143849747667</v>
+        <v>-3.872379602791689</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.168516081631454</v>
+        <v>1.164421780413845</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.05674256479531187</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413248732639</v>
+        <v>3.741324873263902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.832441725771374</v>
+        <v>-3.842677478815395</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.181080322983884</v>
+        <v>1.176986021766276</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.06121269001062524</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481233</v>
+        <v>3.750725801481235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.653066304532606</v>
+        <v>-3.663302057576628</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.246617466785806</v>
+        <v>1.242523165568197</v>
       </c>
       <c r="F1957" t="n">
         <v>0.09556406816009344</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452228</v>
+        <v>3.71698814345223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.698080518053212</v>
+        <v>-3.708316271097234</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.209419236709153</v>
+        <v>1.205324935491544</v>
       </c>
       <c r="F1958" t="n">
         <v>0.06521517284548883</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979535</v>
+        <v>3.737023032979538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.965085028325648</v>
+        <v>-3.975320781369669</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.108308994939124</v>
+        <v>1.104214693721516</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1291478651974597</v>
@@ -46631,10 +46631,10 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.253872248784563</v>
+        <v>-4.264108001828585</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9919980286520598</v>
+        <v>0.9879037274344511</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2302339852964601</v>
@@ -46654,10 +46654,10 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.221396662613791</v>
+        <v>-4.231632415657812</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.002588224674685</v>
+        <v>0.9984939234570769</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2302339852964601</v>
@@ -46677,10 +46677,10 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.202358534906494</v>
+        <v>-4.212594287950515</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.006728194965849</v>
+        <v>1.002633893748241</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.2884175966276546</v>
@@ -46700,10 +46700,10 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.219104400162869</v>
+        <v>-4.22934015320689</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.17761171780198</v>
+        <v>1.173517416584371</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.2884175966276546</v>
@@ -46723,10 +46723,10 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.271424780763661</v>
+        <v>-4.281660533807682</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.157516894547796</v>
+        <v>1.153422593330188</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.2534707366187825</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259125</v>
+        <v>3.787422005259126</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.270947036036747</v>
+        <v>-4.425983439732601</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.163716522835488</v>
+        <v>1.101701961357146</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.2534707366187825</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.393118917395605</v>
+        <v>3.393118917395606</v>
       </c>
       <c r="C1966" t="n">
         <v>2.658449928184302</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.270947036036747</v>
+        <v>-4.425983439732601</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.163716522835488</v>
+        <v>1.101701961357146</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2534707366187825</v>

--- a/tame_output/ON/bt/strategyON_20240516.xlsx
+++ b/tame_output/ON/bt/strategyON_20240516.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>14.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-45.8%</t>
+          <t>-41.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.0%</t>
+          <t>111.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.3%</t>
+          <t>-52.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.4%</t>
+          <t>444.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-604.2%</t>
+          <t>-599.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.3%</t>
+          <t>-38.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>161.2%</t>
+          <t>97.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-266.1%</t>
+          <t>-262.5%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-21.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-180.9%</t>
+          <t>-176.3%</t>
         </is>
       </c>
     </row>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45478,19 +45478,19 @@
         <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.964743835775355</v>
+        <v>2.983588430979907</v>
       </c>
       <c r="D1910" t="n">
         <v>-7.661900678452795</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1003728599195099</v>
+        <v>-0.08152826471495755</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.460727438978569</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.088307372388214</v>
+        <v>2.107151967592766</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723562653879202</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.956029849521877</v>
+        <v>2.974874444726429</v>
       </c>
       <c r="D1911" t="n">
         <v>-7.637672042063822</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.0993953916173993</v>
+        <v>-0.0805507964128469</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.436498802589596</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.094130567968119</v>
+        <v>2.112975163172672</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.949069237426784</v>
+        <v>2.967913832631336</v>
       </c>
       <c r="D1912" t="n">
         <v>-7.594123635293132</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.08893664100421628</v>
+        <v>-0.07009204579966388</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.436498802589596</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.087169955873026</v>
+        <v>2.106014551077579</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.963531591807927</v>
+        <v>2.982376187012479</v>
       </c>
       <c r="D1913" t="n">
         <v>-7.351975241839273</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.02238507075847007</v>
+        <v>0.04122966596302247</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.436498802589596</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.101632310254169</v>
+        <v>2.120476905458722</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.958063712267122</v>
+        <v>2.976908307471674</v>
       </c>
       <c r="D1914" t="n">
         <v>-7.288745870070925</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.04220893992500452</v>
+        <v>0.06105353512955691</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.436498802589596</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.096164430713364</v>
+        <v>2.115009025917917</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.955561806277699</v>
+        <v>2.974406401482251</v>
       </c>
       <c r="D1915" t="n">
         <v>-7.165454735253794</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.08902348786243364</v>
+        <v>0.107868083066986</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.313207667772466</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.167637205614219</v>
+        <v>2.186481800818772</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.963262784515024</v>
+        <v>2.982107379719577</v>
       </c>
       <c r="D1916" t="n">
         <v>-7.144305536350351</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.105184145661136</v>
+        <v>0.1240287408656888</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.292058468869023</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.188027703193611</v>
+        <v>2.206872298398164</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.959043492862075</v>
+        <v>2.977888088066627</v>
       </c>
       <c r="D1917" t="n">
         <v>-6.900540094366907</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1984710308015645</v>
+        <v>0.2173156260061173</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.292058468869023</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.183808411540661</v>
+        <v>2.202653006745214</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.961167806782091</v>
+        <v>2.980012401986643</v>
       </c>
       <c r="D1918" t="n">
         <v>-6.753643066649037</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2593541558087287</v>
+        <v>0.2781987510132815</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.244400226890435</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.21452767064783</v>
+        <v>2.233372265852383</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.953909881765793</v>
+        <v>2.972754476970346</v>
       </c>
       <c r="D1919" t="n">
         <v>-6.503792672699962</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3520363883720603</v>
+        <v>0.3708809835766131</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.244400226890435</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.207269745631532</v>
+        <v>2.226114340836085</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.957509005286441</v>
+        <v>2.976353600490994</v>
       </c>
       <c r="D1920" t="n">
         <v>-6.32790058023253</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.425992348879682</v>
+        <v>0.4448369440842348</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.244400226890435</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.210868869152181</v>
+        <v>2.229713464356734</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780930335862985</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.970836511340995</v>
+        <v>2.989681106545548</v>
       </c>
       <c r="D1921" t="n">
         <v>-6.156454117210067</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5078984401432209</v>
+        <v>0.5267430353477738</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.072953763867972</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.327064253020212</v>
+        <v>2.345908848224765</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376164710278</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.969856988957292</v>
+        <v>2.988701584161845</v>
       </c>
       <c r="D1922" t="n">
         <v>-5.931421117541244</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5969321176270475</v>
+        <v>0.6157767128316003</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.8479207641991487</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.461104530437803</v>
+        <v>2.479949125642356</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.974551790011609</v>
+        <v>2.993396385216162</v>
       </c>
       <c r="D1923" t="n">
         <v>-5.716786739904837</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6874806697359275</v>
+        <v>0.7063252649404803</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.6332863865627419</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.594579958073965</v>
+        <v>2.613424553278517</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.955746048795405</v>
+        <v>2.974590643999958</v>
       </c>
       <c r="D1924" t="n">
         <v>-5.623786698698939</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7058749450020825</v>
+        <v>0.7247195402066353</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.6332863865627419</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.57577421685776</v>
+        <v>2.594618812062313</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.957489125420282</v>
+        <v>2.976333720624835</v>
       </c>
       <c r="D1925" t="n">
         <v>-5.383356201894078</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8037902203489038</v>
+        <v>0.8226348155534566</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.3928558897578817</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.721775591565554</v>
+        <v>2.740620186770107</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.961418439255103</v>
+        <v>2.980263034459655</v>
       </c>
       <c r="D1926" t="n">
         <v>-5.311113633722884</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8366165614522019</v>
+        <v>0.8554611566567547</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.3928558897578817</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.725704905400374</v>
+        <v>2.744549500604927</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.962097023172443</v>
+        <v>2.980941618376995</v>
       </c>
       <c r="D1927" t="n">
         <v>-5.195173784097698</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8836710852196159</v>
+        <v>0.9025156804241687</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.3160341587417578</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.772476527927388</v>
+        <v>2.791321123131941</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.959095094392436</v>
+        <v>2.977939689596989</v>
       </c>
       <c r="D1928" t="n">
         <v>-4.952518195674536</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9777313918088746</v>
+        <v>0.9965759870134274</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.3160341587417578</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.769474599147382</v>
+        <v>2.788319194351935</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.96067413140305</v>
+        <v>2.979518726607603</v>
       </c>
       <c r="D1929" t="n">
         <v>-4.732497397637525</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.067318748034293</v>
+        <v>1.086163343238846</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.1748143136737775</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.855785543198784</v>
+        <v>2.874630138403337</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.976568314204874</v>
+        <v>2.995412909409426</v>
       </c>
       <c r="D1930" t="n">
         <v>-4.599629708574247</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.136360006461427</v>
+        <v>1.15520460166598</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.1748143136737775</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.871679726000608</v>
+        <v>2.89052432120516</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.977714158645175</v>
+        <v>2.996558753849728</v>
       </c>
       <c r="D1931" t="n">
         <v>-4.440114605054878</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.201311892309477</v>
+        <v>1.22015648751403</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.01529921015440761</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.968534632552531</v>
+        <v>2.987379227757084</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791269976046996</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.987802261206615</v>
+        <v>3.006646856411168</v>
       </c>
       <c r="D1932" t="n">
         <v>-4.29544245995514</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.269268852910812</v>
+        <v>1.288113448115365</v>
       </c>
       <c r="F1932" t="n">
         <v>0.1293729349453298</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.065426022173813</v>
+        <v>3.084270617378366</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.973839752608041</v>
+        <v>2.992684347812594</v>
       </c>
       <c r="D1933" t="n">
         <v>-4.355317287312833</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.231356413369161</v>
+        <v>1.250201008573714</v>
       </c>
       <c r="F1933" t="n">
         <v>0.06949810758763769</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.015538617160624</v>
+        <v>3.034383212365177</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762643902144515</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.996240245930607</v>
+        <v>3.01508484113516</v>
       </c>
       <c r="D1934" t="n">
         <v>-4.268517789533824</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.28847670580333</v>
+        <v>1.307321301007883</v>
       </c>
       <c r="F1934" t="n">
         <v>0.06949810758763769</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.03793911048319</v>
+        <v>3.056783705687743</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.996312647304019</v>
+        <v>3.015157242508572</v>
       </c>
       <c r="D1935" t="n">
         <v>-4.27098749599563</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.28756122459202</v>
+        <v>1.306405819796573</v>
       </c>
       <c r="F1935" t="n">
         <v>0.06702840112583153</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.036529687979518</v>
+        <v>3.055374283184071</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.007319569778721</v>
+        <v>3.026164164983274</v>
       </c>
       <c r="D1936" t="n">
         <v>-4.33935768231964</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.271220072537118</v>
+        <v>1.290064667741671</v>
       </c>
       <c r="F1936" t="n">
         <v>0.07630410016204647</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.05310202987595</v>
+        <v>3.071946625080503</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.997756278410613</v>
+        <v>3.016600873615165</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.217941252693164</v>
+        <v>-4.400038211151307</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.3102233530196</v>
+        <v>1.256229164840896</v>
       </c>
       <c r="F1937" t="n">
         <v>0.07630410016204647</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.043538738507841</v>
+        <v>3.062383333712394</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710903155887702</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.822465843450999</v>
+        <v>2.841310438655552</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.248934412021869</v>
+        <v>-4.431031370480012</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.122535654328505</v>
+        <v>1.0685414661498</v>
       </c>
       <c r="F1938" t="n">
         <v>0.07630410016204647</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.868248303548228</v>
+        <v>2.887092898752781</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.7460389506759</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.827033075442787</v>
+        <v>2.84587767064734</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.0734601522294</v>
+        <v>-4.255557110687542</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.19729259023728</v>
+        <v>1.143298402058576</v>
       </c>
       <c r="F1939" t="n">
         <v>0.07630410016204647</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.872815535540016</v>
+        <v>2.891660130744568</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765020747695446</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.802775104203994</v>
+        <v>2.821619699408547</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.184396404870649</v>
+        <v>-4.366493363328791</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.128660117941988</v>
+        <v>1.074665929763283</v>
       </c>
       <c r="F1940" t="n">
         <v>0.07630410016204647</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.848557564301223</v>
+        <v>2.867402159505775</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773206721581291</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.8059064894239</v>
+        <v>2.824751084628453</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.387422982413882</v>
+        <v>-4.569519940872024</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.0505808721446</v>
+        <v>0.9965866839658957</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.1267224773811869</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.729873002995188</v>
+        <v>2.748717598199741</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.816078875856032</v>
+        <v>2.834923471060585</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.229497383478589</v>
+        <v>-4.411594341936731</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.123923498150849</v>
+        <v>1.069929309972145</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.1267224773811869</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.74004538942732</v>
+        <v>2.758889984631873</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786946382212297</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.811025146429893</v>
+        <v>2.829869741634445</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.143253920452211</v>
+        <v>-4.325350878910354</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.153367153935261</v>
+        <v>1.099372965756557</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.1267224773811869</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.734991660001181</v>
+        <v>2.753836255205734</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.802800921874418</v>
+        <v>2.821645517078971</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.144437005103272</v>
+        <v>-4.326533963561415</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.144669695519362</v>
+        <v>1.090675507340658</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.1323655258476985</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.723381606365799</v>
+        <v>2.742226201570352</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.80335279490752</v>
+        <v>2.822197390112072</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.021309298109189</v>
+        <v>-4.203406256567332</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.194472651350097</v>
+        <v>1.140478463171392</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.1323655258476985</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.723933479398901</v>
+        <v>2.742778074603454</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.732625486798885</v>
+        <v>2.751470082003438</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.92849881665833</v>
+        <v>-4.110595775116472</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.160869535821806</v>
+        <v>1.106875347643102</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.0395550443968391</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.708892460160782</v>
+        <v>2.727737055365335</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.734498962723486</v>
+        <v>2.753343557928039</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.8799357644373</v>
+        <v>-4.062032722895442</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.182168232634819</v>
+        <v>1.128174044456115</v>
       </c>
       <c r="F1947" t="n">
         <v>0.009008007824191089</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.739903767418001</v>
+        <v>2.758748362622554</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.729574671235209</v>
+        <v>2.748419266439762</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.76726454620105</v>
+        <v>-3.949361504659192</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.222312428441042</v>
+        <v>1.168318240262338</v>
       </c>
       <c r="F1948" t="n">
         <v>0.1216792260604413</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.802582206871474</v>
+        <v>2.821426802076027</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743044028268537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.735065967065876</v>
+        <v>2.753910562270429</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.654887545018377</v>
+        <v>-3.83698450347652</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.272754524744778</v>
+        <v>1.218760336566074</v>
       </c>
       <c r="F1949" t="n">
         <v>0.1216792260604413</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.808073502702142</v>
+        <v>2.826918097906694</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689594264968862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.746563168834415</v>
+        <v>2.765407764038968</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.853122113905108</v>
+        <v>-4.03521907236325</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.204957898958625</v>
+        <v>1.150963710779921</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.07655534282628929</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.700629963138642</v>
+        <v>2.719474558343195</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643066046175322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.584918888835069</v>
+        <v>2.603763484039622</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.936123394930386</v>
+        <v>-4.118220353388529</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.010113106549167</v>
+        <v>0.9561189183704626</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.09512622735346304</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.527843152422991</v>
+        <v>2.546687747627544</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199268</v>
+        <v>3.682712735199269</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.705068549554274</v>
+        <v>2.723913144758827</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.001281012403902</v>
+        <v>-3.959026081331953</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.104199720278966</v>
+        <v>1.139946287912299</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.09512622735346304</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.647992813142197</v>
+        <v>2.666837408346749</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660768</v>
+        <v>3.733008865660769</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.719581575656597</v>
+        <v>2.73842617086115</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.087879595385006</v>
+        <v>-4.045624664313056</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.084073313188848</v>
+        <v>1.11981988082218</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.09512622735346304</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.66250583924452</v>
+        <v>2.681350434449072</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.741170494383424</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.717001016998966</v>
+        <v>2.735845612203519</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.049495932826855</v>
+        <v>-4.007241001754905</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.096846219554477</v>
+        <v>1.132592787187809</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.05674256479531187</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.682955478121779</v>
+        <v>2.701800073326332</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002484</v>
+        <v>3.751143622002485</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.713730045844268</v>
+        <v>2.732574641048821</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.872379602791689</v>
+        <v>-3.830124671719739</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.164421780413845</v>
+        <v>1.200168348047178</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.05674256479531187</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.679684506967081</v>
+        <v>2.698529102171634</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263902</v>
+        <v>3.741324873263903</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.714413437606181</v>
+        <v>2.733258032810734</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.842677478815395</v>
+        <v>-3.800422547743445</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.176986021766276</v>
+        <v>1.212732589399608</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.06121269001062524</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.677685823599806</v>
+        <v>2.696530418804359</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481235</v>
+        <v>3.750725801481236</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.708200412912595</v>
+        <v>2.727045008117148</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.663302057576628</v>
+        <v>-3.621047126504678</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.242523165568197</v>
+        <v>1.27826973320153</v>
       </c>
       <c r="F1957" t="n">
         <v>0.09556406816009344</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.765538853808652</v>
+        <v>2.784383449013204</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71698814345223</v>
+        <v>3.716988143452231</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.689007868244185</v>
+        <v>2.707852463448738</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.708316271097234</v>
+        <v>-3.666061340025284</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.205324935491544</v>
+        <v>1.241071503124877</v>
       </c>
       <c r="F1958" t="n">
         <v>0.06521517284548883</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.728136971951479</v>
+        <v>2.746981567156031</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737023032979538</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.694699430583131</v>
+        <v>2.713544025787684</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.975320781369669</v>
+        <v>-3.933065850297719</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.104214693721516</v>
+        <v>1.139961261354849</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1291478651974597</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.617210711464655</v>
+        <v>2.636055306669208</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702305879230808</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.693903352479632</v>
+        <v>2.712747947684185</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.264108001828585</v>
+        <v>-4.221853070756635</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9879037274344511</v>
+        <v>1.023650295067784</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2302339852964601</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.555762961301757</v>
+        <v>2.574607556506309</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705568086285454</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.691503314033949</v>
+        <v>2.710347909238502</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.231632415657812</v>
+        <v>-4.189377484585862</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9984939234570769</v>
+        <v>1.03424049109041</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2302339852964601</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.553362922856073</v>
+        <v>2.572207518060626</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709506867848102</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.688028033242194</v>
+        <v>2.706872628446747</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.212594287950515</v>
+        <v>-4.170339356878565</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.002633893748241</v>
+        <v>1.038380461381573</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.2884175966276546</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.514977475265602</v>
+        <v>2.533822070470154</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731060897601251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.865609902180875</v>
+        <v>2.884454497385427</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.22934015320689</v>
+        <v>-4.18708522213494</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.173517416584371</v>
+        <v>1.209263984217704</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.2884175966276546</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.692559344204282</v>
+        <v>2.711403939408835</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722443786537863</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.866443231167008</v>
+        <v>2.885287826371561</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.281660533807682</v>
+        <v>-4.239405602735732</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.153422593330188</v>
+        <v>1.189169160963521</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.2534707366187825</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.714360789195739</v>
+        <v>2.733205384400291</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259126</v>
+        <v>3.787422005259125</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.872451761563934</v>
+        <v>2.891296356768487</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.425983439732601</v>
+        <v>-4.383728508660651</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.101701961357146</v>
+        <v>1.137448528990479</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.2534707366187825</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.720369319592665</v>
+        <v>2.739213914797217</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.393118917395606</v>
+        <v>3.421347928243438</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.658449928184302</v>
+        <v>2.704152823701542</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.425983439732601</v>
+        <v>-4.383728508660651</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.101701961357146</v>
+        <v>1.137448528990479</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2534707366187825</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.65151372517067</v>
+        <v>2.69721662068791</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240516.xlsx
+++ b/tame_output/ON/bt/strategyON_20240516.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -824,52 +824,52 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>55.0%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>26.8%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>42.2%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>26.3%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-41.2%</t>
+          <t>-10.3%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.1%</t>
+          <t>111.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>130.0%</t>
+          <t>130.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.5%</t>
+          <t>-51.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-73.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.7%</t>
+          <t>444.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.2%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-599.9%</t>
+          <t>-572.1%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.6%</t>
+          <t>-41.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>-55.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-262.5%</t>
+          <t>-239.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-188.8%</t>
+          <t>-136.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-249.3%</t>
+          <t>-240.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1461,52 +1461,52 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-176.3%</t>
+          <t>-154.8%</t>
         </is>
       </c>
     </row>
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.74014641518837</v>
+        <v>-10.64081449834258</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.116791437877724</v>
+        <v>-1.077058671139407</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.572337942563149</v>
+        <v>-2.500089520916105</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.636220786973482</v>
+        <v>1.679569839961708</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.45623768425962</v>
+        <v>-10.35690576741383</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9974942412675878</v>
+        <v>-0.9577614745292706</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.572337942563149</v>
+        <v>-2.500089520916105</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.641954491212119</v>
+        <v>1.685303544200345</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.38487129164997</v>
+        <v>-10.28553937480418</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9786849466175935</v>
+        <v>-0.9389521798792773</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.500971549953501</v>
+        <v>-2.428723128306457</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.675037064384042</v>
+        <v>1.718386117372269</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.1210344244459</v>
+        <v>-10.02170250760011</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.883033681048873</v>
+        <v>-0.8433009143105568</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.500971549953501</v>
+        <v>-2.428723128306457</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.665153583071135</v>
+        <v>1.708502636059361</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.853792623577505</v>
+        <v>-9.754460706731713</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7779715212008882</v>
+        <v>-0.7382387544625715</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.500971549953501</v>
+        <v>-2.428723128306457</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.663319022571761</v>
+        <v>1.706668075559987</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781946</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.755885584901014</v>
+        <v>-9.656553668055222</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7391090207037525</v>
+        <v>-0.6993762539654358</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.432985800092944</v>
+        <v>-2.360737378445901</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.703810157514634</v>
+        <v>1.74715921050286</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.731932043925056</v>
+        <v>-9.632600127079264</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.728859098167876</v>
+        <v>-0.6891263314295593</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.409032259116987</v>
+        <v>-2.336783837469943</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.718850788245702</v>
+        <v>1.762199841233928</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487771</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.467872105602259</v>
+        <v>-9.368540188756468</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6364954390005093</v>
+        <v>-0.5967626722621926</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.144972320794191</v>
+        <v>-2.072723899147147</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.864026435077628</v>
+        <v>1.907375488065854</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.760792482097422</v>
+        <v>-8.66146056525163</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3564506232588753</v>
+        <v>-0.3167178565205586</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.144972320794191</v>
+        <v>-2.072723899147147</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.861239401417327</v>
+        <v>1.904588454405553</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.720608183731231</v>
+        <v>-8.62127626688544</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3400332800245578</v>
+        <v>-0.3003005132862411</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.104788022428</v>
+        <v>-2.032539600780956</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.885693604324883</v>
+        <v>1.929042657313109</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.640538388193427</v>
+        <v>-8.541206471347635</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3086385405886789</v>
+        <v>-0.2689057738503622</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.024718226890196</v>
+        <v>-1.952469805243152</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.933102302868322</v>
+        <v>1.976451355856548</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.407057165963828</v>
+        <v>-8.307725249118036</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2073216228589869</v>
+        <v>-0.1675888561206702</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.791237004660597</v>
+        <v>-1.718988583013554</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.081115465043934</v>
+        <v>2.12446451803216</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.257390774956313</v>
+        <v>-8.158058858110522</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1503472767689402</v>
+        <v>-0.1106145100306235</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.698333513418061</v>
+        <v>-1.626085091771018</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.133965349476496</v>
+        <v>2.177314402464722</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.125115301325426</v>
+        <v>-8.025783384479634</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1020696005695583</v>
+        <v>-0.06233683383124156</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.566058039787175</v>
+        <v>-1.493809618140131</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.208698120402055</v>
+        <v>2.252047173390281</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.934515626652273</v>
+        <v>-7.835183709806482</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.02301467001266033</v>
+        <v>0.01671809672565594</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.375458365114022</v>
+        <v>-1.303209943466978</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.325872985893583</v>
+        <v>2.369222038881809</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.685515827968692</v>
+        <v>-7.586183911122901</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.08949159068443047</v>
+        <v>0.1292243574227472</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.375458365114022</v>
+        <v>-1.303209943466978</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.338779327117242</v>
+        <v>2.382128380105468</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.791105817741797</v>
+        <v>-7.691773900896005</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.08072033482402974</v>
+        <v>-0.04098756808571302</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.481048354887126</v>
+        <v>-1.408799933240083</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.147449403654161</v>
+        <v>2.190798456642387</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.809840719860394</v>
+        <v>-7.710508803014602</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.0396699537943821</v>
+        <v>6.281294393417625e-05</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.481048354887126</v>
+        <v>-1.408799933240083</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.195993745531247</v>
+        <v>2.239342798519473</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.983588430979907</v>
+        <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.661900678452795</v>
+        <v>-7.562568761607003</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.08152826471495755</v>
+        <v>-0.06064009318119368</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.460727438978569</v>
+        <v>-1.388479017331525</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.107151967592766</v>
+        <v>2.13165642537644</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723562653879202</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.974874444726429</v>
+        <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.637672042063822</v>
+        <v>-7.53834012521803</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.0805507964128469</v>
+        <v>-0.05966262487908258</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.436498802589596</v>
+        <v>-1.364250380942553</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.112975163172672</v>
+        <v>2.137479620956345</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.967913832631336</v>
+        <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.594123635293132</v>
+        <v>-7.49479171844734</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.07009204579966388</v>
+        <v>-0.04920387426589956</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.436498802589596</v>
+        <v>-1.364250380942553</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.106014551077579</v>
+        <v>2.130519008861252</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.982376187012479</v>
+        <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.351975241839273</v>
+        <v>-7.252643324993482</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.04122966596302247</v>
+        <v>0.06211783749678679</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.436498802589596</v>
+        <v>-1.364250380942553</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.120476905458722</v>
+        <v>2.144981363242395</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.976908307471674</v>
+        <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.288745870070925</v>
+        <v>-7.189413953225134</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.06105353512955691</v>
+        <v>0.08194170666332123</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.436498802589596</v>
+        <v>-1.364250380942553</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.115009025917917</v>
+        <v>2.13951348370159</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.974406401482251</v>
+        <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.165454735253794</v>
+        <v>-7.066122818408003</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.107868083066986</v>
+        <v>0.1287562546007504</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.313207667772466</v>
+        <v>-1.240959246125422</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.186481800818772</v>
+        <v>2.210986258602445</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.982107379719577</v>
+        <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.144305536350351</v>
+        <v>-7.044973619504559</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1240287408656888</v>
+        <v>0.1449169123994527</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.292058468869023</v>
+        <v>-1.219810047221979</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.206872298398164</v>
+        <v>2.231376756181837</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.977888088066627</v>
+        <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.900540094366907</v>
+        <v>-6.801208177521115</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2173156260061173</v>
+        <v>0.2382037975398812</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.292058468869023</v>
+        <v>-1.219810047221979</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.202653006745214</v>
+        <v>2.227157464528887</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.980012401986643</v>
+        <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.753643066649037</v>
+        <v>-6.654311149803245</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2781987510132815</v>
+        <v>0.2990869225470449</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.244400226890435</v>
+        <v>-1.172151805243391</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.233372265852383</v>
+        <v>2.257876723636056</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.972754476970346</v>
+        <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.503792672699962</v>
+        <v>-6.404460755854171</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3708809835766131</v>
+        <v>0.391769155110377</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.244400226890435</v>
+        <v>-1.172151805243391</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.226114340836085</v>
+        <v>2.250618798619759</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.976353600490994</v>
+        <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.32790058023253</v>
+        <v>-6.228568663386739</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4448369440842348</v>
+        <v>0.4657251156179987</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.244400226890435</v>
+        <v>-1.172151805243391</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.229713464356734</v>
+        <v>2.254217922140407</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780930335862985</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.989681106545548</v>
+        <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.156454117210067</v>
+        <v>-6.057122200364275</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5267430353477738</v>
+        <v>0.5476312068815377</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.072953763867972</v>
+        <v>-1.000705342220928</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.345908848224765</v>
+        <v>2.370413306008439</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.988701584161845</v>
+        <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.931421117541244</v>
+        <v>-5.996578511974577</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6157767128316003</v>
+        <v>0.5708691598537139</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8479207641991487</v>
+        <v>-0.9401616538312295</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.479949125642356</v>
+        <v>2.405759996658555</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.993396385216162</v>
+        <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.716786739904837</v>
+        <v>-5.78194413433817</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7063252649404803</v>
+        <v>0.6614177119625939</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6332863865627419</v>
+        <v>-0.7255272761948227</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.613424553278517</v>
+        <v>2.539235424294716</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.974590643999958</v>
+        <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.623786698698939</v>
+        <v>-5.688944093132272</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7247195402066353</v>
+        <v>0.6798119872287489</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6332863865627419</v>
+        <v>-0.7255272761948227</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.594618812062313</v>
+        <v>2.520429683078512</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.976333720624835</v>
+        <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.383356201894078</v>
+        <v>-5.448513596327412</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8226348155534566</v>
+        <v>0.7777272625755707</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.3928558897578817</v>
+        <v>-0.4850967793899624</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.740620186770107</v>
+        <v>2.666431057786305</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.980263034459655</v>
+        <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.311113633722884</v>
+        <v>-5.376271028156217</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8554611566567547</v>
+        <v>0.8105536036788688</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.3928558897578817</v>
+        <v>-0.4850967793899624</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.744549500604927</v>
+        <v>2.670360371621125</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.980941618376995</v>
+        <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.195173784097698</v>
+        <v>-5.260331178531032</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9025156804241687</v>
+        <v>0.8576081274462828</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3160341587417578</v>
+        <v>-0.4082750483738385</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.791321123131941</v>
+        <v>2.71713199414814</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.977939689596989</v>
+        <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.952518195674536</v>
+        <v>-5.017675590107869</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9965759870134274</v>
+        <v>0.9516684340355415</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3160341587417578</v>
+        <v>-0.4082750483738385</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.788319194351935</v>
+        <v>2.714130065368134</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.979518726607603</v>
+        <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.732497397637525</v>
+        <v>-4.797654792070858</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.086163343238846</v>
+        <v>1.04125579026096</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.1748143136737775</v>
+        <v>-0.2670552033058583</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.874630138403337</v>
+        <v>2.800441009419536</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.995412909409426</v>
+        <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.599629708574247</v>
+        <v>-4.664787103007581</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.15520460166598</v>
+        <v>1.110297048688094</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.1748143136737775</v>
+        <v>-0.2670552033058583</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.89052432120516</v>
+        <v>2.816335192221359</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.996558753849728</v>
+        <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.440114605054878</v>
+        <v>-4.505271999488211</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.22015648751403</v>
+        <v>1.175248934536144</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.01529921015440761</v>
+        <v>-0.1075400997864884</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.987379227757084</v>
+        <v>2.913190098773283</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791269976046996</v>
       </c>
       <c r="C1932" t="n">
-        <v>3.006646856411168</v>
+        <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.29544245995514</v>
+        <v>-4.360599854388473</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.288113448115365</v>
+        <v>1.243205895137479</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.1293729349453298</v>
+        <v>0.03713204531324904</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.084270617378366</v>
+        <v>3.010081488394565</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.992684347812594</v>
+        <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.355317287312833</v>
+        <v>-4.420474681746166</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.250201008573714</v>
+        <v>1.205293455595827</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.06949810758763769</v>
+        <v>-0.02274278204444308</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.034383212365177</v>
+        <v>2.960194083381376</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762643902144515</v>
       </c>
       <c r="C1934" t="n">
-        <v>3.01508484113516</v>
+        <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.268517789533824</v>
+        <v>-4.333675183967157</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.307321301007883</v>
+        <v>1.262413748029997</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.06949810758763769</v>
+        <v>-0.02274278204444308</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.056783705687743</v>
+        <v>2.982594576703942</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
-        <v>3.015157242508572</v>
+        <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.27098749599563</v>
+        <v>-4.336144890428963</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.306405819796573</v>
+        <v>1.261498266818687</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.06702840112583153</v>
+        <v>-0.02521248850624924</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.055374283184071</v>
+        <v>2.98118515420027</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.026164164983274</v>
+        <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.33935768231964</v>
+        <v>-4.404515076752974</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.290064667741671</v>
+        <v>1.245157114763785</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.07630410016204647</v>
+        <v>-0.0159367894700343</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.071946625080503</v>
+        <v>2.997757496096701</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.016600873615165</v>
+        <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.400038211151307</v>
+        <v>-4.283098647126497</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.256229164840896</v>
+        <v>1.284160395246267</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.07630410016204647</v>
+        <v>-0.0159367894700343</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.062383333712394</v>
+        <v>2.988194204728592</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710903155887702</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.841310438655552</v>
+        <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.431031370480012</v>
+        <v>-4.314091806455203</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.0685414661498</v>
+        <v>1.096472696555171</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.07630410016204647</v>
+        <v>-0.0159367894700343</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.887092898752781</v>
+        <v>2.812903769768979</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.7460389506759</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.84587767064734</v>
+        <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.255557110687542</v>
+        <v>-4.138617546662733</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.143298402058576</v>
+        <v>1.171229632463947</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.07630410016204647</v>
+        <v>-0.0159367894700343</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.891660130744568</v>
+        <v>2.817471001760767</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765020747695446</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.821619699408547</v>
+        <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.366493363328791</v>
+        <v>-4.249553799303982</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.074665929763283</v>
+        <v>1.102597160168654</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.07630410016204647</v>
+        <v>-0.0159367894700343</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.867402159505775</v>
+        <v>2.793213030521974</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773206721581291</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.824751084628453</v>
+        <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.569519940872024</v>
+        <v>-4.452580376847215</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9965866839658957</v>
+        <v>1.024517914371267</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1267224773811869</v>
+        <v>-0.2189633670132677</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.748717598199741</v>
+        <v>2.674528469215939</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.834923471060585</v>
+        <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.411594341936731</v>
+        <v>-4.294654777911922</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.069929309972145</v>
+        <v>1.097860540377516</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1267224773811869</v>
+        <v>-0.2189633670132677</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.758889984631873</v>
+        <v>2.684700855648072</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786946382212297</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.829869741634445</v>
+        <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.325350878910354</v>
+        <v>-4.208411314885544</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.099372965756557</v>
+        <v>1.127304196161928</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1267224773811869</v>
+        <v>-0.2189633670132677</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.753836255205734</v>
+        <v>2.679647126221932</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.821645517078971</v>
+        <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.326533963561415</v>
+        <v>-4.209594399536606</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.090675507340658</v>
+        <v>1.118606737746028</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1323655258476985</v>
+        <v>-0.2246064154797792</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.742226201570352</v>
+        <v>2.668037072586551</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.822197390112072</v>
+        <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.203406256567332</v>
+        <v>-4.086466692542523</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.140478463171392</v>
+        <v>1.168409693576763</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1323655258476985</v>
+        <v>-0.2246064154797792</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.742778074603454</v>
+        <v>2.668588945619653</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.751470082003438</v>
+        <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.110595775116472</v>
+        <v>-3.993656211091663</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.106875347643102</v>
+        <v>1.134806578048473</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.0395550443968391</v>
+        <v>-0.1317959340289199</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.727737055365335</v>
+        <v>2.653547926381534</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.753343557928039</v>
+        <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.062032722895442</v>
+        <v>-3.945093158870633</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.128174044456115</v>
+        <v>1.156105274861486</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.009008007824191089</v>
+        <v>-0.08323288180788968</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.758748362622554</v>
+        <v>2.684559233638752</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.748419266439762</v>
+        <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.949361504659192</v>
+        <v>-3.832421940634383</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.168318240262338</v>
+        <v>1.196249470667709</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.1216792260604413</v>
+        <v>0.02943833642836052</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.821426802076027</v>
+        <v>2.747237673092226</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743044028268537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.753910562270429</v>
+        <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.83698450347652</v>
+        <v>-3.72004493945171</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.218760336566074</v>
+        <v>1.246691566971445</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.1216792260604413</v>
+        <v>0.02943833642836052</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.826918097906694</v>
+        <v>2.752728968922893</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689594264968862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.765407764038968</v>
+        <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.03521907236325</v>
+        <v>-3.918279508338441</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.150963710779921</v>
+        <v>1.178894941185292</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.07655534282628929</v>
+        <v>-0.1687962324583701</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.719474558343195</v>
+        <v>2.645285429359394</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643066046175322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.603763484039622</v>
+        <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.118220353388529</v>
+        <v>-4.00128078936372</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9561189183704626</v>
+        <v>0.9840501487758335</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.09512622735346304</v>
+        <v>-0.1873671169855438</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.546687747627544</v>
+        <v>2.472498618643743</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682712735199269</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.723913144758827</v>
+        <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.959026081331953</v>
+        <v>-3.842086517307143</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.139946287912299</v>
+        <v>1.16787751831767</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.09512622735346304</v>
+        <v>-0.1873671169855438</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.666837408346749</v>
+        <v>2.592648279362948</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733008865660769</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.73842617086115</v>
+        <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.045624664313056</v>
+        <v>-3.928685100288246</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.11981988082218</v>
+        <v>1.147751111227552</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.09512622735346304</v>
+        <v>-0.1873671169855438</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.681350434449072</v>
+        <v>2.607161305465271</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741170494383424</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.735845612203519</v>
+        <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.007241001754905</v>
+        <v>-3.890301437730095</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.132592787187809</v>
+        <v>1.160524017593181</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.05674256479531187</v>
+        <v>-0.1489834544273926</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.701800073326332</v>
+        <v>2.627610944342531</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751143622002485</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.732574641048821</v>
+        <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.830124671719739</v>
+        <v>-3.713185107694929</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.200168348047178</v>
+        <v>1.228099578452549</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.05674256479531187</v>
+        <v>-0.1489834544273926</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.698529102171634</v>
+        <v>2.624339973187833</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741324873263903</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.733258032810734</v>
+        <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.800422547743445</v>
+        <v>-3.683482983718636</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.212732589399608</v>
+        <v>1.24066381980498</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.06121269001062524</v>
+        <v>-0.153453579642706</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.696530418804359</v>
+        <v>2.622341289820558</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750725801481236</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.727045008117148</v>
+        <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.621047126504678</v>
+        <v>-3.504107562479867</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.27826973320153</v>
+        <v>1.306200963606901</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.09556406816009344</v>
+        <v>0.003323178528012671</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.784383449013204</v>
+        <v>2.710194320029403</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716988143452231</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.707852463448738</v>
+        <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.666061340025284</v>
+        <v>-3.549121776000474</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.241071503124877</v>
+        <v>1.269002733530249</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.06521517284548883</v>
+        <v>-0.02702571678659194</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.746981567156031</v>
+        <v>2.67279243817223</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737023032979538</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.713544025787684</v>
+        <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.933065850297719</v>
+        <v>-3.816126286272909</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.139961261354849</v>
+        <v>1.16789249176022</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1291478651974597</v>
+        <v>-0.2213887548295405</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.636055306669208</v>
+        <v>2.561866177685407</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702305879230808</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.712747947684185</v>
+        <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.221853070756635</v>
+        <v>-4.104913506731824</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.023650295067784</v>
+        <v>1.051581525473155</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2302339852964601</v>
+        <v>-0.3224748749285409</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.574607556506309</v>
+        <v>2.500418427522508</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705568086285454</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.710347909238502</v>
+        <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.189377484585862</v>
+        <v>-4.072437920561052</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.03424049109041</v>
+        <v>1.062171721495781</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2302339852964601</v>
+        <v>-0.3224748749285409</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.572207518060626</v>
+        <v>2.498018389076825</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709506867848102</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.706872628446747</v>
+        <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.170339356878565</v>
+        <v>-4.053399792853755</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.038380461381573</v>
+        <v>1.066311691786945</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2884175966276546</v>
+        <v>-0.3806584862597354</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.533822070470154</v>
+        <v>2.459632941486353</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731060897601251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.884454497385427</v>
+        <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.18708522213494</v>
+        <v>-4.07014565811013</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.209263984217704</v>
+        <v>1.237195214623075</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2884175966276546</v>
+        <v>-0.3806584862597354</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.711403939408835</v>
+        <v>2.637214810425033</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722443786537863</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.885287826371561</v>
+        <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.239405602735732</v>
+        <v>-4.122466038710922</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.189169160963521</v>
+        <v>1.217100391368892</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2534707366187825</v>
+        <v>-0.3457116262508633</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.733205384400291</v>
+        <v>2.65901625541649</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259125</v>
+        <v>3.787422005259123</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.891296356768487</v>
+        <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.383728508660651</v>
+        <v>-4.266788944635841</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.137448528990479</v>
+        <v>1.16537975939585</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.2534707366187825</v>
+        <v>-0.3457116262508633</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.739213914797217</v>
+        <v>2.665024785813416</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.421347928243438</v>
+        <v>3.425851425683921</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.704152823701542</v>
+        <v>3.013062669295287</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.383728508660651</v>
+        <v>-4.10544491719165</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.137448528990479</v>
+        <v>1.37052827810488</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2534707366187825</v>
+        <v>-0.1685146519091816</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.69721662068791</v>
+        <v>2.911953878149779</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240516.xlsx
+++ b/tame_output/ON/bt/strategyON_20240516.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>46.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-24.8%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.0%</t>
+          <t>111.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>130.1%</t>
+          <t>130.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.9%</t>
+          <t>-52.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.2%</t>
+          <t>-73.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.9%</t>
+          <t>448.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.6%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-572.1%</t>
+          <t>-583.3%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,47 +1150,47 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.5%</t>
+          <t>-38.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-55.7%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>162.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-239.2%</t>
+          <t>-258.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-26.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-31.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-20.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-136.2%</t>
+          <t>-190.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-240.8%</t>
+          <t>-247.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,37 +1476,37 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-154.8%</t>
+          <t>-173.4%</t>
         </is>
       </c>
     </row>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969594</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923088</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.4900556660786</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.64081449834258</v>
+        <v>-10.74014641518837</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.077058671139407</v>
+        <v>-1.116791437877724</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.500089520916105</v>
+        <v>-2.572337942563149</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.679569839961708</v>
+        <v>1.636220786973482</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081565</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.35690576741383</v>
+        <v>-10.45623768425962</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9577614745292706</v>
+        <v>-0.9974942412675878</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.500089520916105</v>
+        <v>-2.572337942563149</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.685303544200345</v>
+        <v>1.641954491212119</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.28553937480418</v>
+        <v>-10.38487129164997</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9389521798792773</v>
+        <v>-0.9786849466175935</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.428723128306457</v>
+        <v>-2.500971549953501</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.718386117372269</v>
+        <v>1.675037064384042</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.02170250760011</v>
+        <v>-10.1210344244459</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8433009143105568</v>
+        <v>-0.883033681048873</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.428723128306457</v>
+        <v>-2.500971549953501</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.708502636059361</v>
+        <v>1.665153583071135</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.754460706731713</v>
+        <v>-9.853792623577505</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7382387544625715</v>
+        <v>-0.7779715212008882</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.428723128306457</v>
+        <v>-2.500971549953501</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.706668075559987</v>
+        <v>1.663319022571761</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.656553668055222</v>
+        <v>-9.755885584901014</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6993762539654358</v>
+        <v>-0.7391090207037525</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.360737378445901</v>
+        <v>-2.432985800092944</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.74715921050286</v>
+        <v>1.703810157514634</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.632600127079264</v>
+        <v>-9.731932043925056</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6891263314295593</v>
+        <v>-0.728859098167876</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.336783837469943</v>
+        <v>-2.409032259116987</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.762199841233928</v>
+        <v>1.718850788245702</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.368540188756468</v>
+        <v>-9.467872105602259</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5967626722621926</v>
+        <v>-0.6364954390005093</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.072723899147147</v>
+        <v>-2.144972320794191</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.907375488065854</v>
+        <v>1.864026435077628</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309724</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.66146056525163</v>
+        <v>-8.760792482097422</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3167178565205586</v>
+        <v>-0.3564506232588753</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.072723899147147</v>
+        <v>-2.144972320794191</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.904588454405553</v>
+        <v>1.861239401417327</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858727</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.62127626688544</v>
+        <v>-8.720608183731231</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3003005132862411</v>
+        <v>-0.3400332800245578</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.032539600780956</v>
+        <v>-2.104788022428</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.929042657313109</v>
+        <v>1.885693604324883</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.541206471347635</v>
+        <v>-8.640538388193427</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2689057738503622</v>
+        <v>-0.3086385405886789</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.952469805243152</v>
+        <v>-2.024718226890196</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.976451355856548</v>
+        <v>1.933102302868322</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.307725249118036</v>
+        <v>-8.407057165963828</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1675888561206702</v>
+        <v>-0.2073216228589869</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.718988583013554</v>
+        <v>-1.791237004660597</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.12446451803216</v>
+        <v>2.081115465043934</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.158058858110522</v>
+        <v>-8.257390774956313</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1106145100306235</v>
+        <v>-0.1503472767689402</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.626085091771018</v>
+        <v>-1.698333513418061</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.177314402464722</v>
+        <v>2.133965349476496</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860428</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.025783384479634</v>
+        <v>-8.125115301325426</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.06233683383124156</v>
+        <v>-0.1020696005695583</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.493809618140131</v>
+        <v>-1.566058039787175</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.252047173390281</v>
+        <v>2.208698120402055</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.835183709806482</v>
+        <v>-7.934515626652273</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.01671809672565594</v>
+        <v>-0.02301467001266033</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.303209943466978</v>
+        <v>-1.375458365114022</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.369222038881809</v>
+        <v>2.325872985893583</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.586183911122901</v>
+        <v>-7.685515827968692</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1292243574227472</v>
+        <v>0.08949159068443047</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.303209943466978</v>
+        <v>-1.375458365114022</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.382128380105468</v>
+        <v>2.338779327117242</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.691773900896005</v>
+        <v>-7.791105817741797</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.04098756808571302</v>
+        <v>-0.08072033482402974</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.408799933240083</v>
+        <v>-1.481048354887126</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.190798456642387</v>
+        <v>2.147449403654161</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.710508803014602</v>
+        <v>-7.809840719860394</v>
       </c>
       <c r="E1909" t="n">
-        <v>6.281294393417625e-05</v>
+        <v>-0.0396699537943821</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.408799933240083</v>
+        <v>-1.481048354887126</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.239342798519473</v>
+        <v>2.195993745531247</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.562568761607003</v>
+        <v>-7.661900678452795</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.06064009318119368</v>
+        <v>-0.1003728599195099</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.388479017331525</v>
+        <v>-1.460727438978569</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.13165642537644</v>
+        <v>2.088307372388214</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.53834012521803</v>
+        <v>-7.637672042063822</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.05966262487908258</v>
+        <v>-0.0993953916173993</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.364250380942553</v>
+        <v>-1.436498802589596</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.137479620956345</v>
+        <v>2.094130567968119</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.49479171844734</v>
+        <v>-7.594123635293132</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.04920387426589956</v>
+        <v>-0.08893664100421628</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.364250380942553</v>
+        <v>-1.436498802589596</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.130519008861252</v>
+        <v>2.087169955873026</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.252643324993482</v>
+        <v>-7.351975241839273</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.06211783749678679</v>
+        <v>0.02238507075847007</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.364250380942553</v>
+        <v>-1.436498802589596</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.144981363242395</v>
+        <v>2.101632310254169</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.189413953225134</v>
+        <v>-7.288745870070925</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.08194170666332123</v>
+        <v>0.04220893992500452</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.364250380942553</v>
+        <v>-1.436498802589596</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.13951348370159</v>
+        <v>2.096164430713364</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.066122818408003</v>
+        <v>-7.165454735253794</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1287562546007504</v>
+        <v>0.08902348786243364</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.240959246125422</v>
+        <v>-1.313207667772466</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.210986258602445</v>
+        <v>2.167637205614219</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.044973619504559</v>
+        <v>-7.144305536350351</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1449169123994527</v>
+        <v>0.105184145661136</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.219810047221979</v>
+        <v>-1.292058468869023</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.231376756181837</v>
+        <v>2.188027703193611</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.801208177521115</v>
+        <v>-6.900540094366907</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2382037975398812</v>
+        <v>0.1984710308015645</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.219810047221979</v>
+        <v>-1.292058468869023</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.227157464528887</v>
+        <v>2.183808411540661</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.654311149803245</v>
+        <v>-6.753643066649037</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2990869225470449</v>
+        <v>0.2593541558087287</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.172151805243391</v>
+        <v>-1.244400226890435</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.257876723636056</v>
+        <v>2.21452767064783</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.404460755854171</v>
+        <v>-6.503792672699962</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.391769155110377</v>
+        <v>0.3520363883720603</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.172151805243391</v>
+        <v>-1.244400226890435</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.250618798619759</v>
+        <v>2.207269745631532</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.228568663386739</v>
+        <v>-6.32790058023253</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4657251156179987</v>
+        <v>0.425992348879682</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.172151805243391</v>
+        <v>-1.244400226890435</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.254217922140407</v>
+        <v>2.210868869152181</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862985</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.057122200364275</v>
+        <v>-6.156454117210067</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5476312068815377</v>
+        <v>0.5078984401432209</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.000705342220928</v>
+        <v>-1.072953763867972</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.370413306008439</v>
+        <v>2.327064253020212</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.996578511974577</v>
+        <v>-5.931421117541244</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5708691598537139</v>
+        <v>0.5969321176270475</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9401616538312295</v>
+        <v>-0.8479207641991487</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.405759996658555</v>
+        <v>2.461104530437803</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.78194413433817</v>
+        <v>-5.716786739904837</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6614177119625939</v>
+        <v>0.6874806697359275</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7255272761948227</v>
+        <v>-0.6332863865627419</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.539235424294716</v>
+        <v>2.594579958073965</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.688944093132272</v>
+        <v>-5.623786698698939</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6798119872287489</v>
+        <v>0.7058749450020825</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7255272761948227</v>
+        <v>-0.6332863865627419</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.520429683078512</v>
+        <v>2.57577421685776</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.448513596327412</v>
+        <v>-5.383356201894078</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7777272625755707</v>
+        <v>0.8037902203489038</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4850967793899624</v>
+        <v>-0.3928558897578817</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.666431057786305</v>
+        <v>2.721775591565554</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.376271028156217</v>
+        <v>-5.311113633722884</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8105536036788688</v>
+        <v>0.8366165614522019</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4850967793899624</v>
+        <v>-0.3928558897578817</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.670360371621125</v>
+        <v>2.725704905400374</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.260331178531032</v>
+        <v>-5.195173784097698</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8576081274462828</v>
+        <v>0.8836710852196159</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4082750483738385</v>
+        <v>-0.3160341587417578</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.71713199414814</v>
+        <v>2.772476527927388</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.017675590107869</v>
+        <v>-4.952518195674536</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9516684340355415</v>
+        <v>0.9777313918088746</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4082750483738385</v>
+        <v>-0.3160341587417578</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.714130065368134</v>
+        <v>2.769474599147382</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.797654792070858</v>
+        <v>-4.732497397637525</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.04125579026096</v>
+        <v>1.067318748034293</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2670552033058583</v>
+        <v>-0.1748143136737775</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.800441009419536</v>
+        <v>2.855785543198784</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.664787103007581</v>
+        <v>-4.599629708574247</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.110297048688094</v>
+        <v>1.136360006461427</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2670552033058583</v>
+        <v>-0.1748143136737775</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.816335192221359</v>
+        <v>2.871679726000608</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966258</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.505271999488211</v>
+        <v>-4.440114605054878</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.175248934536144</v>
+        <v>1.201311892309477</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1075400997864884</v>
+        <v>-0.01529921015440761</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.913190098773283</v>
+        <v>2.968534632552531</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046996</v>
+        <v>3.791269976046995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.360599854388473</v>
+        <v>-4.29544245995514</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.243205895137479</v>
+        <v>1.269268852910812</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.03713204531324904</v>
+        <v>0.1293729349453298</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.010081488394565</v>
+        <v>3.065426022173813</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.420474681746166</v>
+        <v>-4.355317287312833</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.205293455595827</v>
+        <v>1.231356413369161</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.02274278204444308</v>
+        <v>0.06949810758763769</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.960194083381376</v>
+        <v>3.015538617160624</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144515</v>
+        <v>3.762643902144514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.333675183967157</v>
+        <v>-4.268517789533824</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.262413748029997</v>
+        <v>1.28847670580333</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.02274278204444308</v>
+        <v>0.06949810758763769</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.982594576703942</v>
+        <v>3.03793911048319</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.729142822900692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.336144890428963</v>
+        <v>-4.27098749599563</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.261498266818687</v>
+        <v>1.28756122459202</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.02521248850624924</v>
+        <v>0.06702840112583153</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.98118515420027</v>
+        <v>3.036529687979518</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432166204736</v>
+        <v>3.743216620473599</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.404515076752974</v>
+        <v>-4.33935768231964</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.245157114763785</v>
+        <v>1.271220072537118</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.0159367894700343</v>
+        <v>0.07630410016204647</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.997757496096701</v>
+        <v>3.05310202987595</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.714175563978368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.283098647126497</v>
+        <v>-4.217941252693164</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.284160395246267</v>
+        <v>1.3102233530196</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.0159367894700343</v>
+        <v>0.07630410016204647</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.988194204728592</v>
+        <v>3.043538738507841</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.314091806455203</v>
+        <v>-4.248934412021869</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.096472696555171</v>
+        <v>1.122535654328505</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.0159367894700343</v>
+        <v>0.07630410016204647</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.812903769768979</v>
+        <v>2.868248303548228</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.138617546662733</v>
+        <v>-4.0734601522294</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.171229632463947</v>
+        <v>1.19729259023728</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.0159367894700343</v>
+        <v>0.07630410016204647</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.817471001760767</v>
+        <v>2.872815535540016</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695446</v>
+        <v>3.765020747695445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.249553799303982</v>
+        <v>-4.184396404870649</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.102597160168654</v>
+        <v>1.128660117941988</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.0159367894700343</v>
+        <v>0.07630410016204647</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.793213030521974</v>
+        <v>2.848557564301223</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581291</v>
+        <v>3.77320672158129</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.452580376847215</v>
+        <v>-4.387422982413882</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.024517914371267</v>
+        <v>1.0505808721446</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2189633670132677</v>
+        <v>-0.1267224773811869</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.674528469215939</v>
+        <v>2.729873002995188</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.294654777911922</v>
+        <v>-4.229497383478589</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.097860540377516</v>
+        <v>1.123923498150849</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2189633670132677</v>
+        <v>-0.1267224773811869</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.684700855648072</v>
+        <v>2.74004538942732</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212297</v>
+        <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.208411314885544</v>
+        <v>-4.143253920452211</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.127304196161928</v>
+        <v>1.153367153935261</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2189633670132677</v>
+        <v>-0.1267224773811869</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.679647126221932</v>
+        <v>2.734991660001181</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.752023923786043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.209594399536606</v>
+        <v>-4.144437005103272</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.118606737746028</v>
+        <v>1.144669695519362</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2246064154797792</v>
+        <v>-0.1323655258476985</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.668037072586551</v>
+        <v>2.723381606365799</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.086466692542523</v>
+        <v>-4.021309298109189</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.168409693576763</v>
+        <v>1.194472651350097</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2246064154797792</v>
+        <v>-0.1323655258476985</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.668588945619653</v>
+        <v>2.723933479398901</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.993656211091663</v>
+        <v>-3.92849881665833</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.134806578048473</v>
+        <v>1.160869535821806</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1317959340289199</v>
+        <v>-0.0395550443968391</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.653547926381534</v>
+        <v>2.708892460160782</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.945093158870633</v>
+        <v>-3.8799357644373</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.156105274861486</v>
+        <v>1.182168232634819</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.08323288180788968</v>
+        <v>0.009008007824191089</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.684559233638752</v>
+        <v>2.739903767418001</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.832421940634383</v>
+        <v>-3.76726454620105</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.196249470667709</v>
+        <v>1.222312428441042</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.02943833642836052</v>
+        <v>0.1216792260604413</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.747237673092226</v>
+        <v>2.802582206871474</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268537</v>
+        <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.72004493945171</v>
+        <v>-3.654887545018377</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.246691566971445</v>
+        <v>1.272754524744778</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.02943833642836052</v>
+        <v>0.1216792260604413</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.752728968922893</v>
+        <v>2.808073502702142</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968862</v>
+        <v>3.689594264968861</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.918279508338441</v>
+        <v>-3.853122113905108</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.178894941185292</v>
+        <v>1.204957898958625</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1687962324583701</v>
+        <v>-0.07655534282628929</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.645285429359394</v>
+        <v>2.700629963138642</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175322</v>
+        <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.00128078936372</v>
+        <v>-3.936123394930386</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9840501487758335</v>
+        <v>1.010113106549167</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1873671169855438</v>
+        <v>-0.09512622735346304</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.472498618643743</v>
+        <v>2.527843152422991</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199269</v>
+        <v>3.682712735199268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.842086517307143</v>
+        <v>-3.77692912287381</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.16787751831767</v>
+        <v>1.193940476091003</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1873671169855438</v>
+        <v>-0.09512622735346304</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.592648279362948</v>
+        <v>2.647992813142197</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660769</v>
+        <v>3.733008865660767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.928685100288246</v>
+        <v>-3.785894465162742</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.147751111227552</v>
+        <v>1.204867365277753</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1873671169855438</v>
+        <v>-0.09512622735346304</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.607161305465271</v>
+        <v>2.66250583924452</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383424</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.890301437730095</v>
+        <v>-3.747510802604591</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.160524017593181</v>
+        <v>1.217640271643382</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1489834544273926</v>
+        <v>-0.05674256479531187</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.627610944342531</v>
+        <v>2.682955478121779</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002485</v>
+        <v>3.751143622002483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.713185107694929</v>
+        <v>-3.570394472569425</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.228099578452549</v>
+        <v>1.285215832502751</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1489834544273926</v>
+        <v>-0.05674256479531187</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.624339973187833</v>
+        <v>2.679684506967081</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263903</v>
+        <v>3.741324873263901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.683482983718636</v>
+        <v>-3.540692348593131</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.24066381980498</v>
+        <v>1.297780073855181</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.153453579642706</v>
+        <v>-0.06121269001062524</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.622341289820558</v>
+        <v>2.677685823599806</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481236</v>
+        <v>3.750725801481235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.504107562479867</v>
+        <v>-3.361316927354363</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.306200963606901</v>
+        <v>1.363317217657103</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.003323178528012671</v>
+        <v>0.09556406816009344</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.710194320029403</v>
+        <v>2.765538853808652</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452231</v>
+        <v>3.71698814345223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.549121776000474</v>
+        <v>-3.40633114087497</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.269002733530249</v>
+        <v>1.32611898758045</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.02702571678659194</v>
+        <v>0.06521517284548883</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.67279243817223</v>
+        <v>2.728136971951479</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979538</v>
+        <v>3.737023032979537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.816126286272909</v>
+        <v>-3.673335651147405</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.16789249176022</v>
+        <v>1.225008745810422</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2213887548295405</v>
+        <v>-0.1291478651974597</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.561866177685407</v>
+        <v>2.617210711464655</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230808</v>
+        <v>3.702305879230806</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.104913506731824</v>
+        <v>-3.96212287160632</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.051581525473155</v>
+        <v>1.108697779523357</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3224748749285409</v>
+        <v>-0.2302339852964601</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.500418427522508</v>
+        <v>2.555762961301757</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285454</v>
+        <v>3.705568086285452</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.072437920561052</v>
+        <v>-3.929647285435548</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.062171721495781</v>
+        <v>1.119287975545983</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3224748749285409</v>
+        <v>-0.2302339852964601</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.498018389076825</v>
+        <v>2.553362922856073</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848102</v>
+        <v>3.7095068678481</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.053399792853755</v>
+        <v>-3.910609157728251</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.066311691786945</v>
+        <v>1.123427945837146</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3806584862597354</v>
+        <v>-0.2884175966276546</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.459632941486353</v>
+        <v>2.514977475265602</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601251</v>
+        <v>3.73106089760125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.07014565811013</v>
+        <v>-3.927355022984626</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.237195214623075</v>
+        <v>1.294311468673277</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3806584862597354</v>
+        <v>-0.2884175966276546</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.637214810425033</v>
+        <v>2.692559344204282</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537863</v>
+        <v>3.722443786537862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.122466038710922</v>
+        <v>-3.979675403585418</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.217100391368892</v>
+        <v>1.274216645419094</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3457116262508633</v>
+        <v>-0.2534707366187825</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.65901625541649</v>
+        <v>2.714360789195739</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259123</v>
+        <v>3.787422005259121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.266788944635841</v>
+        <v>-4.123998309510337</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.16537975939585</v>
+        <v>1.222496013446052</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3457116262508633</v>
+        <v>-0.2534707366187825</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.665024785813416</v>
+        <v>2.720369319592665</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.425851425683921</v>
+        <v>3.744050984640675</v>
       </c>
       <c r="C1966" t="n">
-        <v>3.013062669295287</v>
+        <v>2.868742162766486</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.10544491719165</v>
+        <v>-4.217590364186178</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.37052827810488</v>
+        <v>1.181349592778267</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1685146519091816</v>
+        <v>-0.2371619937844121</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.911953878149779</v>
+        <v>2.726444966495839</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240516.xlsx
+++ b/tame_output/ON/bt/strategyON_20240516.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>49.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.2%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>130.0%</t>
+          <t>129.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-670.7%</t>
+          <t>-664.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.5%</t>
+          <t>-52.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.7%</t>
+          <t>-73.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.9%</t>
+          <t>449.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-10.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-583.3%</t>
+          <t>-574.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-268.7%</t>
+          <t>-266.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.7%</t>
+          <t>-38.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-148.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>162.2%</t>
+          <t>87.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-258.1%</t>
+          <t>-254.5%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.7%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.5%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-190.0%</t>
+          <t>-189.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-247.7%</t>
+          <t>-249.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-173.4%</t>
+          <t>-174.5%</t>
         </is>
       </c>
     </row>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.425085676122209</v>
+        <v>-4.357616925061445</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.367347951800749</v>
+        <v>1.394335452225054</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.555734532842116</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.856891469271996</v>
+        <v>-4.789422718211233</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.180958522008238</v>
+        <v>1.207946022432544</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.692152029283383</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.091585463404549</v>
+        <v>-5.024116712343785</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.075365699357308</v>
+        <v>1.102353199781613</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.6858157620541279</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.427248110635001</v>
+        <v>-5.359779359574238</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9396812321210919</v>
+        <v>0.9666687325453975</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.6858157620541279</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.790874355535315</v>
+        <v>-5.723405604474551</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.800718294395208</v>
+        <v>0.8277057948195137</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.7840373989212537</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.156001738174061</v>
+        <v>-6.088532987113298</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6539218563455407</v>
+        <v>0.6809093567698463</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.080348183220266</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.564590515354739</v>
+        <v>-6.497121764293976</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4892478894880288</v>
+        <v>0.516235389912334</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.488936960400945</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.977572999495833</v>
+        <v>-6.910104248435069</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3192403283030516</v>
+        <v>0.3462278287273572</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.488936960400945</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.393964873782831</v>
+        <v>-7.326496122722067</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1506776291971299</v>
+        <v>0.1776651296214355</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.488936960400945</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.770641884312675</v>
+        <v>-7.703173133251911</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.01026551565387113</v>
+        <v>0.03725301607817677</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.488936960400945</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.116516706297483</v>
+        <v>-8.04904795523672</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1319848479943571</v>
+        <v>-0.1049973475700514</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.280096584481868</v>
+        <v>-8.212627833421104</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1990118792131095</v>
+        <v>-0.1720243787888043</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.576757926292066</v>
+        <v>-8.509289175231302</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3138974400079806</v>
+        <v>-0.2869099395836754</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.700002315507495</v>
+        <v>-8.632533564446732</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3672215002285557</v>
+        <v>-0.3402339998042501</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.083003704250126</v>
+        <v>-9.015534953189363</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.5205241570471921</v>
+        <v>-0.4935366566228865</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.240402584463247</v>
+        <v>-9.172933833402483</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5809121931610104</v>
+        <v>-0.5539246927367047</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.715078976347944</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.599932906967249</v>
+        <v>-9.532464155906485</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7193740188645608</v>
+        <v>-0.6923865184402551</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.715078976347944</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.650281970421471</v>
+        <v>-9.582813219360707</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7315976242890723</v>
+        <v>-0.7046101238647666</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.765428039802166</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.869430938495668</v>
+        <v>-9.801962187434905</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.816215460896982</v>
+        <v>-0.7892279604726768</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.984577007876364</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.865740013539257</v>
+        <v>-9.798271262478494</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8147390909144181</v>
+        <v>-0.7877515904901125</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.984577007876364</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.06999818886912</v>
+        <v>-10.00252943780836</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.890929163927721</v>
+        <v>-0.8639416635034154</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.112215952490353</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.2880359605003</v>
+        <v>-10.22056720943954</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9736617180957556</v>
+        <v>-0.9466742176714509</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.286986720586252</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.21456612883285</v>
+        <v>-10.14709737777209</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.9289020839353554</v>
+        <v>-0.9019145835110498</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.213516888918803</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.38969054621939</v>
+        <v>-10.32222179515863</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9843966301424558</v>
+        <v>-0.9574091297181502</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.388641306305347</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.62414264023388</v>
+        <v>-10.55667388917312</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.085396632649848</v>
+        <v>-1.058409132225542</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.388641306305347</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.91194648477112</v>
+        <v>-10.84447773371036</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.207190361238719</v>
+        <v>-1.180202860814414</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.676445150842585</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.96473264037145</v>
+        <v>-10.89726388931068</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.227189033640293</v>
+        <v>-1.200201533215989</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.772120637424982</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.19676156010771</v>
+        <v>-11.12929280904695</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.317306872905684</v>
+        <v>-1.290319372481378</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.834133334613405</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.1447460461389</v>
+        <v>-11.07727729507813</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.292510331631758</v>
+        <v>-1.265522831207452</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.834133334613405</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.28641788786302</v>
+        <v>-11.21894913680225</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.350654295220147</v>
+        <v>-1.323666794795842</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.834133334613405</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.23682704343818</v>
+        <v>-11.16935829237742</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.315764547285342</v>
+        <v>-1.288777046861036</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.784542490188572</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.03767493620108</v>
+        <v>-10.97020618514032</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.249154838037185</v>
+        <v>-1.222167337612879</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.619219964238758</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.81182978348167</v>
+        <v>-10.74436103242091</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.149237703913212</v>
+        <v>-1.122250203488906</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.577293288651595</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.68725112714408</v>
+        <v>-10.61978237608332</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.098267096822117</v>
+        <v>-1.07127959639781</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.577293288651595</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.74014641518837</v>
+        <v>-10.6726776641276</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.116791437877724</v>
+        <v>-1.089803937453417</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.572337942563149</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.45623768425962</v>
+        <v>-10.38876893319885</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9974942412675878</v>
+        <v>-0.9705067408432813</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.572337942563149</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.38487129164997</v>
+        <v>-10.31740254058921</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9786849466175935</v>
+        <v>-0.9516974461932879</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.500971549953501</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.1210344244459</v>
+        <v>-10.05356567338514</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.883033681048873</v>
+        <v>-0.8560461806245674</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.500971549953501</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.853792623577505</v>
+        <v>-9.786323872516739</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7779715212008882</v>
+        <v>-0.7509840207765817</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.500971549953501</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.755885584901014</v>
+        <v>-9.688416833840249</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7391090207037525</v>
+        <v>-0.7121215202794464</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.432985800092944</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.731932043925056</v>
+        <v>-9.664463292864291</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.728859098167876</v>
+        <v>-0.7018715977435694</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.409032259116987</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.467872105602259</v>
+        <v>-9.400403354541494</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6364954390005093</v>
+        <v>-0.6095079385762032</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.144972320794191</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.760792482097422</v>
+        <v>-8.693323731036656</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3564506232588753</v>
+        <v>-0.3294631228345688</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.144972320794191</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.720608183731231</v>
+        <v>-8.653139432670466</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3400332800245578</v>
+        <v>-0.3130457796002513</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.104788022428</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.640538388193427</v>
+        <v>-8.573069637132662</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3086385405886789</v>
+        <v>-0.2816510401643728</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.024718226890196</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.407057165963828</v>
+        <v>-8.339588414903062</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2073216228589869</v>
+        <v>-0.1803341224346804</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.791237004660597</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.257390774956313</v>
+        <v>-8.189922023895548</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1503472767689402</v>
+        <v>-0.1233597763446341</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.698333513418061</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.125115301325426</v>
+        <v>-8.057646550264661</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1020696005695583</v>
+        <v>-0.07508210014525218</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.566058039787175</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.934515626652273</v>
+        <v>-7.867046875591508</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.02301467001266033</v>
+        <v>0.003972830411645756</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.375458365114022</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.685515827968692</v>
+        <v>-7.618047076907927</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.08949159068443047</v>
+        <v>0.116479091108737</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.375458365114022</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.791105817741797</v>
+        <v>-7.723637066681031</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.08072033482402974</v>
+        <v>-0.05373283439972365</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.481048354887126</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.809840719860394</v>
+        <v>-7.742371968799628</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.0396699537943821</v>
+        <v>-0.01268245337007601</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.481048354887126</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.661900678452795</v>
+        <v>-7.594431927392029</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1003728599195099</v>
+        <v>-0.07338535949520386</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.460727438978569</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.637672042063822</v>
+        <v>-7.570203291003057</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.0993953916173993</v>
+        <v>-0.07240789119309321</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.436498802589596</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.594123635293132</v>
+        <v>-7.526654884232366</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.08893664100421628</v>
+        <v>-0.06194914057991019</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.436498802589596</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.351975241839273</v>
+        <v>-7.284506490778508</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.02238507075847007</v>
+        <v>0.04937257118277616</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.436498802589596</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.288745870070925</v>
+        <v>-7.22127711901016</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.04220893992500452</v>
+        <v>0.06919644034931061</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.436498802589596</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.165454735253794</v>
+        <v>-7.097985984193029</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.08902348786243364</v>
+        <v>0.1160109882867397</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.313207667772466</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.144305536350351</v>
+        <v>-7.076836785289585</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.105184145661136</v>
+        <v>0.1321716460854425</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.292058468869023</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.900540094366907</v>
+        <v>-6.833071343306141</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1984710308015645</v>
+        <v>0.2254585312258706</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.292058468869023</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.753643066649037</v>
+        <v>-6.686174315588271</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2593541558087287</v>
+        <v>0.2863416562330348</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.244400226890435</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.503792672699962</v>
+        <v>-6.436323921639197</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3520363883720603</v>
+        <v>0.3790238887963668</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.244400226890435</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.32790058023253</v>
+        <v>-6.260431829171765</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.425992348879682</v>
+        <v>0.452979849303988</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.244400226890435</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.156454117210067</v>
+        <v>-6.088985366149301</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5078984401432209</v>
+        <v>0.5348859405675275</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.072953763867972</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.931421117541244</v>
+        <v>-5.863952366480478</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5969321176270475</v>
+        <v>0.6239196180513535</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.8479207641991487</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.716786739904837</v>
+        <v>-5.649317988844071</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6874806697359275</v>
+        <v>0.7144681701602336</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.6332863865627419</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.623786698698939</v>
+        <v>-5.556317947638173</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7058749450020825</v>
+        <v>0.7328624454263886</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.6332863865627419</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.383356201894078</v>
+        <v>-5.315887450833313</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8037902203489038</v>
+        <v>0.8307777207732099</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.3928558897578817</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.311113633722884</v>
+        <v>-5.243644882662118</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8366165614522019</v>
+        <v>0.863604061876508</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.3928558897578817</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.195173784097698</v>
+        <v>-5.127705033036933</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8836710852196159</v>
+        <v>0.910658585643922</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.3160341587417578</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.952518195674536</v>
+        <v>-4.88504944461377</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9777313918088746</v>
+        <v>1.004718892233181</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.3160341587417578</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.732497397637525</v>
+        <v>-4.66502864657676</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.067318748034293</v>
+        <v>1.094306248458599</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.1748143136737775</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.599629708574247</v>
+        <v>-4.532160957513482</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.136360006461427</v>
+        <v>1.163347506885734</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.1748143136737775</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.440114605054878</v>
+        <v>-4.372645853994112</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.201311892309477</v>
+        <v>1.228299392733783</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.01529921015440761</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.29544245995514</v>
+        <v>-4.227973708894375</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.269268852910812</v>
+        <v>1.296256353335118</v>
       </c>
       <c r="F1932" t="n">
         <v>0.1293729349453298</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.355317287312833</v>
+        <v>-4.287848536252067</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.231356413369161</v>
+        <v>1.258343913793467</v>
       </c>
       <c r="F1933" t="n">
         <v>0.06949810758763769</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.268517789533824</v>
+        <v>-4.201049038473059</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.28847670580333</v>
+        <v>1.315464206227636</v>
       </c>
       <c r="F1934" t="n">
         <v>0.06949810758763769</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.27098749599563</v>
+        <v>-4.203518744934865</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.28756122459202</v>
+        <v>1.314548725016326</v>
       </c>
       <c r="F1935" t="n">
         <v>0.06702840112583153</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.33935768231964</v>
+        <v>-4.271888931258875</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.271220072537118</v>
+        <v>1.298207572961424</v>
       </c>
       <c r="F1936" t="n">
         <v>0.07630410016204647</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.217941252693164</v>
+        <v>-4.150472501632398</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.3102233530196</v>
+        <v>1.337210853443906</v>
       </c>
       <c r="F1937" t="n">
         <v>0.07630410016204647</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.248934412021869</v>
+        <v>-4.181465660961104</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.122535654328505</v>
+        <v>1.149523154752811</v>
       </c>
       <c r="F1938" t="n">
         <v>0.07630410016204647</v>
@@ -46148,10 +46148,10 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.0734601522294</v>
+        <v>-4.005991401168634</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.19729259023728</v>
+        <v>1.224280090661586</v>
       </c>
       <c r="F1939" t="n">
         <v>0.07630410016204647</v>
@@ -46171,10 +46171,10 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.184396404870649</v>
+        <v>-4.116927653809883</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.128660117941988</v>
+        <v>1.155647618366294</v>
       </c>
       <c r="F1940" t="n">
         <v>0.07630410016204647</v>
@@ -46194,10 +46194,10 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.387422982413882</v>
+        <v>-4.319954231353116</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.0505808721446</v>
+        <v>1.077568372568906</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.1267224773811869</v>
@@ -46217,10 +46217,10 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.229497383478589</v>
+        <v>-4.162028632417823</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.123923498150849</v>
+        <v>1.150910998575156</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.1267224773811869</v>
@@ -46240,10 +46240,10 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.143253920452211</v>
+        <v>-4.075785169391446</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.153367153935261</v>
+        <v>1.180354654359567</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.1267224773811869</v>
@@ -46263,10 +46263,10 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.144437005103272</v>
+        <v>-4.076968254042507</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.144669695519362</v>
+        <v>1.171657195943668</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.1323655258476985</v>
@@ -46286,10 +46286,10 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.021309298109189</v>
+        <v>-3.953840547048424</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.194472651350097</v>
+        <v>1.221460151774403</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.1323655258476985</v>
@@ -46309,10 +46309,10 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.92849881665833</v>
+        <v>-3.861030065597565</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.160869535821806</v>
+        <v>1.187857036246112</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.0395550443968391</v>
@@ -46332,10 +46332,10 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.8799357644373</v>
+        <v>-3.812467013376534</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.182168232634819</v>
+        <v>1.209155733059125</v>
       </c>
       <c r="F1947" t="n">
         <v>0.009008007824191089</v>
@@ -46355,10 +46355,10 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.76726454620105</v>
+        <v>-3.699795795140284</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.222312428441042</v>
+        <v>1.249299928865348</v>
       </c>
       <c r="F1948" t="n">
         <v>0.1216792260604413</v>
@@ -46378,10 +46378,10 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.654887545018377</v>
+        <v>-3.587418793957612</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.272754524744778</v>
+        <v>1.299742025169084</v>
       </c>
       <c r="F1949" t="n">
         <v>0.1216792260604413</v>
@@ -46401,10 +46401,10 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.853122113905108</v>
+        <v>-3.785653362844342</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.204957898958625</v>
+        <v>1.231945399382931</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.07655534282628929</v>
@@ -46424,10 +46424,10 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.936123394930386</v>
+        <v>-3.868654643869621</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.010113106549167</v>
+        <v>1.037100606973473</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.09512622735346304</v>
@@ -46447,10 +46447,10 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.77692912287381</v>
+        <v>-3.709460371813045</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.193940476091003</v>
+        <v>1.220927976515309</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.09512622735346304</v>
@@ -46470,10 +46470,10 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.785894465162742</v>
+        <v>-3.718425714101977</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.204867365277753</v>
+        <v>1.231854865702059</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.09512622735346304</v>
@@ -46493,10 +46493,10 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.747510802604591</v>
+        <v>-3.680042051543825</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.217640271643382</v>
+        <v>1.244627772067689</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.05674256479531187</v>
@@ -46516,10 +46516,10 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.570394472569425</v>
+        <v>-3.502925721508659</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.285215832502751</v>
+        <v>1.312203332927057</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.05674256479531187</v>
@@ -46539,10 +46539,10 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.540692348593131</v>
+        <v>-3.473223597532366</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.297780073855181</v>
+        <v>1.324767574279488</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.06121269001062524</v>
@@ -46562,10 +46562,10 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.361316927354363</v>
+        <v>-3.293848176293598</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.363317217657103</v>
+        <v>1.390304718081409</v>
       </c>
       <c r="F1957" t="n">
         <v>0.09556406816009344</v>
@@ -46585,10 +46585,10 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.40633114087497</v>
+        <v>-3.338862389814204</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.32611898758045</v>
+        <v>1.353106488004756</v>
       </c>
       <c r="F1958" t="n">
         <v>0.06521517284548883</v>
@@ -46608,10 +46608,10 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.673335651147405</v>
+        <v>-3.60586690008664</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.225008745810422</v>
+        <v>1.251996246234728</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1291478651974597</v>
@@ -46631,10 +46631,10 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.96212287160632</v>
+        <v>-3.894654120545555</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.108697779523357</v>
+        <v>1.135685279947663</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2302339852964601</v>
@@ -46654,10 +46654,10 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.929647285435548</v>
+        <v>-3.862178534374783</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.119287975545983</v>
+        <v>1.146275475970289</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2302339852964601</v>
@@ -46677,10 +46677,10 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.910609157728251</v>
+        <v>-3.843140406667485</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.123427945837146</v>
+        <v>1.150415446261452</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.2884175966276546</v>
@@ -46700,10 +46700,10 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.927355022984626</v>
+        <v>-3.859886271923861</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.294311468673277</v>
+        <v>1.321298969097583</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.2884175966276546</v>
@@ -46723,10 +46723,10 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.979675403585418</v>
+        <v>-3.912206652524652</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.274216645419094</v>
+        <v>1.3012041458434</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.2534707366187825</v>
@@ -46746,10 +46746,10 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.123998309510337</v>
+        <v>-4.056529558449571</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.222496013446052</v>
+        <v>1.249483513870358</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.2534707366187825</v>
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.744050984640675</v>
+        <v>3.779670630087256</v>
       </c>
       <c r="C1966" t="n">
         <v>2.868742162766486</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.217590364186178</v>
+        <v>-4.127262820144697</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.181349592778267</v>
+        <v>1.21748061039486</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2371619937844121</v>
+        <v>-0.2551766238602872</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.726444966495839</v>
+        <v>2.715636188450314</v>
       </c>
     </row>
   </sheetData>
